--- a/Data/Csv/EnemyData.xlsx
+++ b/Data/Csv/EnemyData.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20357"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E076972-3534-443A-88F8-4002A5D48C91}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB02C21-C54C-4F0D-8100-7A3AF67116FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,12 +15,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="8">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -58,26 +61,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>0.0f</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>800.0f</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>100.0f</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1500.0f</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2000.0f</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>移動可能範囲</t>
     <rPh sb="0" eb="2">
       <t>イドウ</t>
@@ -89,14 +72,6 @@
   </si>
   <si>
     <t>1000.0f</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1500.0f</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2000.0f</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -185,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -198,6 +173,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -479,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="12.125" customWidth="1"/>
@@ -510,7 +488,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -523,17 +501,17 @@
       <c r="C2" s="1">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
+      <c r="D2" s="5">
+        <v>-547</v>
+      </c>
+      <c r="E2" s="5">
+        <v>2529.81</v>
+      </c>
+      <c r="F2" s="5">
+        <v>441.197</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -546,17 +524,17 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
+      <c r="D3" s="5">
+        <v>594.33900000000006</v>
+      </c>
+      <c r="E3" s="5">
+        <v>2502.5700000000002</v>
+      </c>
+      <c r="F3" s="5">
+        <v>524.47</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -569,17 +547,385 @@
       <c r="C4" s="1">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="5">
+        <v>728.40800000000002</v>
+      </c>
+      <c r="E4" s="5">
+        <v>2492.4699999999998</v>
+      </c>
+      <c r="F4" s="5">
+        <v>-388.41699999999997</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5">
+        <v>-163.25200000000001</v>
+      </c>
+      <c r="E5" s="5">
+        <v>2463.69</v>
+      </c>
+      <c r="F5" s="5">
+        <v>-908.52599999999995</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>-1104.3</v>
+      </c>
+      <c r="E6" s="5">
+        <v>2283.4</v>
+      </c>
+      <c r="F6" s="5">
+        <v>-675.71</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="B7" s="1">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-1766.17</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1300.7</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1428.11</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-514.99099999999999</v>
+      </c>
+      <c r="E8" s="5">
+        <v>1192.5999999999999</v>
+      </c>
+      <c r="F8" s="5">
+        <v>2277.27</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1654.27</v>
+      </c>
+      <c r="E9" s="5">
+        <v>1225.1300000000001</v>
+      </c>
+      <c r="F9" s="5">
+        <v>1627.67</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1250.32</v>
+      </c>
+      <c r="E10" s="5">
+        <v>608.51300000000003</v>
+      </c>
+      <c r="F10" s="5">
+        <v>2219.7600000000002</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="B11" s="1">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>2530.5100000000002</v>
+      </c>
+      <c r="E11" s="5">
+        <v>177.72300000000001</v>
+      </c>
+      <c r="F11" s="5">
+        <v>643.654</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2416.39</v>
+      </c>
+      <c r="E12" s="5">
+        <v>981.61699999999996</v>
+      </c>
+      <c r="F12" s="5">
+        <v>-302.625</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1701.94</v>
+      </c>
+      <c r="E13" s="5">
+        <v>162.47800000000001</v>
+      </c>
+      <c r="F13" s="5">
+        <v>-1979.66</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-642.40899999999999</v>
+      </c>
+      <c r="E14" s="5">
+        <v>-1884.94</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1721.06</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="1">
         <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1197.5</v>
+      </c>
+      <c r="E15" s="5">
+        <v>-1667.39</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1628.72</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-1731.29</v>
+      </c>
+      <c r="E16" s="5">
+        <v>-1777.48</v>
+      </c>
+      <c r="F16" s="5">
+        <v>852.75099999999998</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-364.67500000000001</v>
+      </c>
+      <c r="E17" s="5">
+        <v>-2541.92</v>
+      </c>
+      <c r="F17" s="5">
+        <v>556.58299999999997</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-1192.8800000000001</v>
+      </c>
+      <c r="E18" s="5">
+        <v>-2283.06</v>
+      </c>
+      <c r="F18" s="5">
+        <v>-510.976</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-1763.13</v>
+      </c>
+      <c r="E19" s="5">
+        <v>-1469.39</v>
+      </c>
+      <c r="F19" s="5">
+        <v>-1288.82</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-724.54100000000005</v>
+      </c>
+      <c r="E20" s="5">
+        <v>-2020.35</v>
+      </c>
+      <c r="F20" s="5">
+        <v>-1505.46</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Csv/EnemyData.xlsx
+++ b/Data/Csv/EnemyData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB02C21-C54C-4F0D-8100-7A3AF67116FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FF9031-F1D5-4999-A2A7-921933A20D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="1575" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -502,13 +502,13 @@
         <v>2</v>
       </c>
       <c r="D2" s="5">
-        <v>-547</v>
+        <v>1423</v>
       </c>
       <c r="E2" s="5">
-        <v>2529.81</v>
+        <v>226</v>
       </c>
       <c r="F2" s="5">
-        <v>441.197</v>
+        <v>-472</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>7</v>
@@ -525,13 +525,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="5">
-        <v>594.33900000000006</v>
+        <v>1290</v>
       </c>
       <c r="E3" s="5">
-        <v>2502.5700000000002</v>
+        <v>-515</v>
       </c>
       <c r="F3" s="5">
-        <v>524.47</v>
+        <v>-1026</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>7</v>
@@ -548,13 +548,13 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>728.40800000000002</v>
+        <v>1163</v>
       </c>
       <c r="E4" s="5">
-        <v>2492.4699999999998</v>
+        <v>-1168</v>
       </c>
       <c r="F4" s="5">
-        <v>-388.41699999999997</v>
+        <v>105</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>7</v>
@@ -571,13 +571,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="5">
-        <v>-163.25200000000001</v>
+        <v>986</v>
       </c>
       <c r="E5" s="5">
-        <v>2463.69</v>
+        <v>-665</v>
       </c>
       <c r="F5" s="5">
-        <v>-908.52599999999995</v>
+        <v>1376</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>7</v>
@@ -594,13 +594,13 @@
         <v>2</v>
       </c>
       <c r="D6" s="5">
-        <v>-1104.3</v>
+        <v>1231</v>
       </c>
       <c r="E6" s="5">
-        <v>2283.4</v>
+        <v>260</v>
       </c>
       <c r="F6" s="5">
-        <v>-675.71</v>
+        <v>1009</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>7</v>
@@ -617,13 +617,13 @@
         <v>2</v>
       </c>
       <c r="D7" s="5">
-        <v>-1766.17</v>
+        <v>166</v>
       </c>
       <c r="E7" s="5">
-        <v>1300.7</v>
+        <v>-146</v>
       </c>
       <c r="F7" s="5">
-        <v>1428.11</v>
+        <v>-1767</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>7</v>
@@ -640,13 +640,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="5">
-        <v>-514.99099999999999</v>
+        <v>243</v>
       </c>
       <c r="E8" s="5">
-        <v>1192.5999999999999</v>
+        <v>-1082</v>
       </c>
       <c r="F8" s="5">
-        <v>2277.27</v>
+        <v>-1681</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>7</v>
@@ -663,13 +663,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="5">
-        <v>1654.27</v>
+        <v>-46</v>
       </c>
       <c r="E9" s="5">
-        <v>1225.1300000000001</v>
+        <v>1284</v>
       </c>
       <c r="F9" s="5">
-        <v>1627.67</v>
+        <v>-152</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>7</v>
@@ -686,13 +686,13 @@
         <v>2</v>
       </c>
       <c r="D10" s="5">
-        <v>1250.32</v>
+        <v>493</v>
       </c>
       <c r="E10" s="5">
-        <v>608.51300000000003</v>
+        <v>900</v>
       </c>
       <c r="F10" s="5">
-        <v>2219.7600000000002</v>
+        <v>-1001</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>7</v>
@@ -709,13 +709,13 @@
         <v>2</v>
       </c>
       <c r="D11" s="5">
-        <v>2530.5100000000002</v>
+        <v>-484</v>
       </c>
       <c r="E11" s="5">
-        <v>177.72300000000001</v>
+        <v>831</v>
       </c>
       <c r="F11" s="5">
-        <v>643.654</v>
+        <v>1638</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>7</v>
@@ -732,13 +732,13 @@
         <v>2</v>
       </c>
       <c r="D12" s="5">
-        <v>2416.39</v>
+        <v>-377</v>
       </c>
       <c r="E12" s="5">
-        <v>981.61699999999996</v>
+        <v>76</v>
       </c>
       <c r="F12" s="5">
-        <v>-302.625</v>
+        <v>1672</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>7</v>
@@ -755,13 +755,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="5">
-        <v>1701.94</v>
+        <v>-72</v>
       </c>
       <c r="E13" s="5">
-        <v>162.47800000000001</v>
+        <v>-1180</v>
       </c>
       <c r="F13" s="5">
-        <v>-1979.66</v>
+        <v>797</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>7</v>
@@ -778,13 +778,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="5">
-        <v>-642.40899999999999</v>
+        <v>51</v>
       </c>
       <c r="E14" s="5">
-        <v>-1884.94</v>
+        <v>-1820</v>
       </c>
       <c r="F14" s="5">
-        <v>1721.06</v>
+        <v>-349</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>7</v>
@@ -801,13 +801,13 @@
         <v>2</v>
       </c>
       <c r="D15" s="5">
-        <v>1197.5</v>
+        <v>-161</v>
       </c>
       <c r="E15" s="5">
-        <v>-1667.39</v>
+        <v>181</v>
       </c>
       <c r="F15" s="5">
-        <v>1628.72</v>
+        <v>-603</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>7</v>
@@ -824,13 +824,13 @@
         <v>2</v>
       </c>
       <c r="D16" s="5">
-        <v>-1731.29</v>
+        <v>-1461</v>
       </c>
       <c r="E16" s="5">
-        <v>-1777.48</v>
+        <v>434</v>
       </c>
       <c r="F16" s="5">
-        <v>852.75099999999998</v>
+        <v>879</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>7</v>
@@ -847,13 +847,13 @@
         <v>2</v>
       </c>
       <c r="D17" s="5">
-        <v>-364.67500000000001</v>
+        <v>-842</v>
       </c>
       <c r="E17" s="5">
-        <v>-2541.92</v>
+        <v>1047</v>
       </c>
       <c r="F17" s="5">
-        <v>556.58299999999997</v>
+        <v>1239</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>7</v>
@@ -870,13 +870,13 @@
         <v>2</v>
       </c>
       <c r="D18" s="5">
-        <v>-1192.8800000000001</v>
+        <v>511</v>
       </c>
       <c r="E18" s="5">
-        <v>-2283.06</v>
+        <v>1299</v>
       </c>
       <c r="F18" s="5">
-        <v>-510.976</v>
+        <v>232</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>7</v>
@@ -893,13 +893,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="5">
-        <v>-1763.13</v>
+        <v>-765</v>
       </c>
       <c r="E19" s="5">
-        <v>-1469.39</v>
+        <v>1365</v>
       </c>
       <c r="F19" s="5">
-        <v>-1288.82</v>
+        <v>408</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>7</v>
@@ -916,13 +916,13 @@
         <v>2</v>
       </c>
       <c r="D20" s="5">
-        <v>-724.54100000000005</v>
+        <v>-847</v>
       </c>
       <c r="E20" s="5">
-        <v>-2020.35</v>
+        <v>1126</v>
       </c>
       <c r="F20" s="5">
-        <v>-1505.46</v>
+        <v>-102</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>7</v>

--- a/Data/Csv/EnemyData.xlsx
+++ b/Data/Csv/EnemyData.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FF9031-F1D5-4999-A2A7-921933A20D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283D4ADE-1260-4C5D-AB81-793358970358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="1575" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -68,10 +68,6 @@
     <rPh sb="2" eb="6">
       <t>カノウハンイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1000.0f</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -160,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -176,6 +172,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -502,16 +513,16 @@
         <v>2</v>
       </c>
       <c r="D2" s="5">
-        <v>1423</v>
+        <v>-1163</v>
       </c>
       <c r="E2" s="5">
-        <v>226</v>
+        <v>10</v>
       </c>
       <c r="F2" s="5">
-        <v>-472</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>7</v>
+        <v>-3758</v>
+      </c>
+      <c r="G2" s="4">
+        <v>1000</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -525,16 +536,16 @@
         <v>2</v>
       </c>
       <c r="D3" s="5">
-        <v>1290</v>
+        <v>-4909</v>
       </c>
       <c r="E3" s="5">
-        <v>-515</v>
+        <v>10</v>
       </c>
       <c r="F3" s="5">
-        <v>-1026</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>7</v>
+        <v>-2436</v>
+      </c>
+      <c r="G3" s="4">
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -548,16 +559,16 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>1163</v>
+        <v>1223</v>
       </c>
       <c r="E4" s="5">
-        <v>-1168</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5">
-        <v>105</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>7</v>
+        <v>-2163</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -571,16 +582,16 @@
         <v>2</v>
       </c>
       <c r="D5" s="5">
-        <v>986</v>
+        <v>4464</v>
       </c>
       <c r="E5" s="5">
-        <v>-665</v>
+        <v>10</v>
       </c>
       <c r="F5" s="5">
-        <v>1376</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>7</v>
+        <v>642</v>
+      </c>
+      <c r="G5" s="4">
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -594,16 +605,16 @@
         <v>2</v>
       </c>
       <c r="D6" s="5">
-        <v>1231</v>
+        <v>-2750</v>
       </c>
       <c r="E6" s="5">
-        <v>260</v>
+        <v>10</v>
       </c>
       <c r="F6" s="5">
-        <v>1009</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>7</v>
+        <v>1218</v>
+      </c>
+      <c r="G6" s="4">
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -617,39 +628,39 @@
         <v>2</v>
       </c>
       <c r="D7" s="5">
-        <v>166</v>
+        <v>-454</v>
       </c>
       <c r="E7" s="5">
-        <v>-146</v>
+        <v>10</v>
       </c>
       <c r="F7" s="5">
-        <v>-1767</v>
-      </c>
-      <c r="G7" s="4" t="s">
+        <v>4495</v>
+      </c>
+      <c r="G7" s="4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2</v>
-      </c>
-      <c r="D8" s="5">
-        <v>243</v>
-      </c>
-      <c r="E8" s="5">
-        <v>-1082</v>
-      </c>
-      <c r="F8" s="5">
-        <v>-1681</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>7</v>
+      <c r="B8" s="6">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>2687</v>
+      </c>
+      <c r="E8" s="7">
+        <v>10</v>
+      </c>
+      <c r="F8" s="7">
+        <v>3286</v>
+      </c>
+      <c r="G8" s="4">
+        <v>1000</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -663,270 +674,116 @@
         <v>2</v>
       </c>
       <c r="D9" s="5">
-        <v>-46</v>
+        <v>-389</v>
       </c>
       <c r="E9" s="5">
-        <v>1284</v>
+        <v>10</v>
       </c>
       <c r="F9" s="5">
-        <v>-152</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>7</v>
+        <v>1347</v>
+      </c>
+      <c r="G9" s="4">
+        <v>1000</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5">
-        <v>493</v>
-      </c>
-      <c r="E10" s="5">
-        <v>900</v>
-      </c>
-      <c r="F10" s="5">
-        <v>-1001</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
-        <v>0</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-484</v>
-      </c>
-      <c r="E11" s="5">
-        <v>831</v>
-      </c>
-      <c r="F11" s="5">
-        <v>1638</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0</v>
-      </c>
-      <c r="C12" s="1">
-        <v>2</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-377</v>
-      </c>
-      <c r="E12" s="5">
-        <v>76</v>
-      </c>
-      <c r="F12" s="5">
-        <v>1672</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0</v>
-      </c>
-      <c r="C13" s="1">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-72</v>
-      </c>
-      <c r="E13" s="5">
-        <v>-1180</v>
-      </c>
-      <c r="F13" s="5">
-        <v>797</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1">
-        <v>2</v>
-      </c>
-      <c r="D14" s="5">
-        <v>51</v>
-      </c>
-      <c r="E14" s="5">
-        <v>-1820</v>
-      </c>
-      <c r="F14" s="5">
-        <v>-349</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0</v>
-      </c>
-      <c r="C15" s="1">
-        <v>2</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-161</v>
-      </c>
-      <c r="E15" s="5">
-        <v>181</v>
-      </c>
-      <c r="F15" s="5">
-        <v>-603</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1">
-        <v>0</v>
-      </c>
-      <c r="C16" s="1">
-        <v>2</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-1461</v>
-      </c>
-      <c r="E16" s="5">
-        <v>434</v>
-      </c>
-      <c r="F16" s="5">
-        <v>879</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="10"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1">
-        <v>0</v>
-      </c>
-      <c r="C17" s="1">
-        <v>2</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-842</v>
-      </c>
-      <c r="E17" s="5">
-        <v>1047</v>
-      </c>
-      <c r="F17" s="5">
-        <v>1239</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1">
-        <v>0</v>
-      </c>
-      <c r="C18" s="1">
-        <v>2</v>
-      </c>
-      <c r="D18" s="5">
-        <v>511</v>
-      </c>
-      <c r="E18" s="5">
-        <v>1299</v>
-      </c>
-      <c r="F18" s="5">
-        <v>232</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0</v>
-      </c>
-      <c r="C19" s="1">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-765</v>
-      </c>
-      <c r="E19" s="5">
-        <v>1365</v>
-      </c>
-      <c r="F19" s="5">
-        <v>408</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1">
-        <v>0</v>
-      </c>
-      <c r="C20" s="1">
-        <v>2</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-847</v>
-      </c>
-      <c r="E20" s="5">
-        <v>1126</v>
-      </c>
-      <c r="F20" s="5">
-        <v>-102</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
